--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="PiggyBank" sheetId="1" r:id="rId1"/>
@@ -250,7 +255,7 @@
     <t>小罐子</t>
   </si>
   <si>
-    <t>1990000_597000</t>
+    <t>1990000_28888800</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
@@ -259,7 +264,7 @@
     <t>中罐子</t>
   </si>
   <si>
-    <t>1990000_2997000</t>
+    <t>1990000_88888800</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
@@ -268,7 +273,7 @@
     <t>大罐子</t>
   </si>
   <si>
-    <t>1990000_8997000</t>
+    <t>1990000_128888800</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
@@ -284,7 +289,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,6 +298,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -300,6 +306,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -449,12 +470,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -801,154 +822,160 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1292,216 +1319,217 @@
   <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="25.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="7.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.25" customWidth="1"/>
+    <col min="9" max="9" width="10.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.25" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="2" t="s">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:11">
+      <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:11">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="2"/>
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:11">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="3"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>1.99</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>1500</v>
       </c>
-      <c r="F5" s="1">
-        <v>597000</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="F5" s="2">
+        <v>28888800</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
-      <c r="I5" s="1">
-        <v>29850</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="I5" s="2">
+        <v>288888</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
         <v>9.99</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>3500</v>
       </c>
-      <c r="F6" s="1">
-        <v>2997000</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="F6" s="2">
+        <v>88888800</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
-      <c r="I6" s="1">
-        <v>299700</v>
-      </c>
-      <c r="J6" s="1" t="s">
+      <c r="I6" s="2">
+        <v>888888</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K6"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="2">
         <v>24.99</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>5000</v>
       </c>
-      <c r="F7" s="1">
-        <v>8997000</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="F7" s="2">
+        <v>128888800</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H7">
         <v>3</v>
       </c>
-      <c r="I7" s="1">
-        <v>1169610</v>
-      </c>
-      <c r="J7" s="1" t="s">
+      <c r="I7" s="2">
+        <v>1288888</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K7"/>
